--- a/assets/files/lit-review-matrix-template.xlsx
+++ b/assets/files/lit-review-matrix-template.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="columns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quotes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="columns" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -473,12 +474,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>explanatory</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>treatment_measure</t>
+          <t>explanatory_measure</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -513,15 +514,10 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>quotes</t>
+          <t>related_articles</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>related_articles</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
@@ -538,7 +534,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -620,24 +651,24 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>explanatory</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>The main explanatory variable, treatment, or exposure</t>
+          <t>The main explanatory variable</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>treatment_measure</t>
+          <t>explanatory_measure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>How the paper measures the treatment or exposure</t>
+          <t>How the paper measures the explanatory variable</t>
         </is>
       </c>
     </row>
@@ -716,36 +747,67 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>quotes</t>
+          <t>related_articles</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Rare in economics, but if the paper has a killer phrase, write it down with its page number</t>
+          <t>Other papers in your matrix that this one builds on, replicates, or contradicts. Linking papers is an art, not a science</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>related_articles</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Other papers in your matrix that this one builds on, replicates, or contradicts. Linking papers is an art, not a science</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
           <t>Anything else, including how the paper relates to your own project</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>quotes sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The citation, exactly as it appears in the matrix sheet, so that you can match each quote to its paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The page number of the quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>One quote, word for word. A paper with three quotes gets three rows</t>
         </is>
       </c>
     </row>

--- a/assets/files/lit-review-matrix-template.xlsx
+++ b/assets/files/lit-review-matrix-template.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The empirical method. In applied microeconomics this is typically the identification strategy: panel data with fixed effects, instrumental variables, a natural experiment, regression discontinuity, a randomized trial</t>
+          <t>The identification strategy: fixed effects, instrumental variables, regression discontinuity, a natural experiment, or a randomized trial (for a trial, describe the treatment)</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>The named datasets: a Demographic and Health Survey, a census, administrative records, or the authors' own survey</t>
+          <t>The datasets: a Demographic and Health Survey, a census, administrative records, or the authors' own survey</t>
         </is>
       </c>
     </row>
